--- a/output/pdf_financials_xlsx/VRB.xlsx
+++ b/output/pdf_financials_xlsx/VRB.xlsx
@@ -6177,25 +6177,25 @@
         <v>6.191639</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>6.42085</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>7.238414</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>7.356063</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>7.964527</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>8.584477</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>9.278703</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>10.735762</v>
       </c>
       <c r="M92" s="3" t="n">
         <v>12.375503</v>
@@ -6828,13 +6828,13 @@
         <v>-0.096305</v>
       </c>
       <c r="N103" s="3" t="n">
-        <v>0</v>
+        <v>0.07823099999999999</v>
       </c>
       <c r="O103" s="3" t="n">
-        <v>0</v>
+        <v>0.009063</v>
       </c>
       <c r="P103" s="3" t="n">
-        <v>0</v>
+        <v>0.017383</v>
       </c>
       <c r="Q103" s="3" t="n">
         <v>0</v>
@@ -7011,13 +7011,13 @@
         <v>-0.09360400000000001</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>0.149661</v>
+        <v>0.227892</v>
       </c>
       <c r="O106" s="3" t="n">
-        <v>0.305998</v>
+        <v>0.315061</v>
       </c>
       <c r="P106" s="3" t="n">
-        <v>0.315652</v>
+        <v>0.333035</v>
       </c>
       <c r="Q106" s="3" t="n">
         <v>-0.32582</v>
@@ -7719,46 +7719,46 @@
         <v>1.171721</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0.792641</v>
+        <v>0.464645</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0.341198</v>
+        <v>0.13865</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-0.358742</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-0.234625</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0.324326</v>
+        <v>0.187554</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-0.104235</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0.000122</v>
+        <v>-0.131004</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>-1.561291</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>-1.329861</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0</v>
+        <v>-0.23834</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0</v>
+        <v>-0.131709</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>0</v>
+        <v>-0.473603</v>
       </c>
       <c r="R118" s="3" t="n">
-        <v>0</v>
+        <v>-0.607519</v>
       </c>
       <c r="S118" s="3" t="n">
-        <v>0</v>
+        <v>-0.118365</v>
       </c>
     </row>
     <row r="119">
@@ -13880,7 +13880,11 @@
           <t>Prepaid and deposits</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -16766,7 +16770,11 @@
           <t>SHARE-BASED PAYMENTS RESERVE</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>-</t>
@@ -19216,7 +19224,11 @@
           <t>SHARE BASED PAYMENTS RESERVE</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
@@ -20350,7 +20362,11 @@
           <t>RESERVE</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
           <t>-</t>
@@ -23492,7 +23508,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
           <t>-</t>
@@ -27116,7 +27136,11 @@
           <t>Exploration and evaluation expenditures, net</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E177" t="inlineStr">
         <is>
           <t>-</t>
@@ -28384,7 +28408,11 @@
           <t>Prepaid and deposits</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E189" t="inlineStr">
         <is>
           <t>-</t>
@@ -29338,7 +29366,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr"/>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
           <t>-</t>
@@ -30064,7 +30096,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr"/>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E205" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/VRB.xlsx
+++ b/output/pdf_financials_xlsx/VRB.xlsx
@@ -1059,22 +1059,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.055339</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.003444</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000642</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.001305</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.004077</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.000328</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -2072,22 +2072,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-3.163949</v>
+        <v>-3.219288</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.873088</v>
+        <v>-1.876532</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-4.46166</v>
+        <v>-4.462302</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-4.77277</v>
+        <v>-4.774075</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-3.335119</v>
+        <v>-3.339196</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-2.376426</v>
+        <v>-2.376754</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-0.440141</v>
@@ -2194,22 +2194,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-3.163949</v>
+        <v>-3.219288</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.873088</v>
+        <v>-1.876532</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-4.46166</v>
+        <v>-4.462302</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-4.77277</v>
+        <v>-4.774075</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-3.335119</v>
+        <v>-3.339196</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-2.366112</v>
+        <v>-2.36644</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-0.438715</v>
@@ -2535,40 +2535,40 @@
         <v>0.528912</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.653717</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.419483</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.148563</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.379855</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.040201</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.795004</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.439647</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.029111</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.614007</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.513682</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.01536</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>0.199237</v>
       </c>
     </row>
     <row r="35">
@@ -2657,40 +2657,40 @@
         <v>0.531296</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.028762</v>
+        <v>0.6824789999999999</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.024689</v>
+        <v>0.444172</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.02834</v>
+        <v>0.176903</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.023</v>
+        <v>0.402855</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.023</v>
+        <v>0.06320099999999999</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.023</v>
+        <v>0.818004</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.023</v>
+        <v>0.462647</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.023</v>
+        <v>0.052111</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.614007</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.513682</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.01536</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>0.199237</v>
       </c>
     </row>
     <row r="37">
@@ -3389,40 +3389,40 @@
         <v>0.013007</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.661664</v>
+        <v>0.007946999999999999</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.448857</v>
+        <v>0.029374</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.165017</v>
+        <v>0.016454</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.406078</v>
+        <v>0.026223</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.065958</v>
+        <v>0.025757</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.917066</v>
+        <v>0.122062</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.483478</v>
+        <v>0.043831</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.06387900000000001</v>
+        <v>0.034768</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.631392</v>
+        <v>0.017385</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.963407</v>
+        <v>0.449725</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.140723</v>
+        <v>0.125363</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>0.319295</v>
+        <v>0.120058</v>
       </c>
     </row>
     <row r="49">
@@ -8992,7 +8992,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -12120,7 +12120,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -15370,7 +15370,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -62914,7 +62914,7 @@
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E520" s="5" t="n">

--- a/output/pdf_financials_xlsx/VRB.xlsx
+++ b/output/pdf_financials_xlsx/VRB.xlsx
@@ -7344,7 +7344,7 @@
         <v>0</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.002617</v>
       </c>
       <c r="D112" s="3" t="n">
         <v>0</v>
@@ -7356,7 +7356,7 @@
         <v>0</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.007529</v>
       </c>
       <c r="H112" s="3" t="n">
         <v>0</v>
@@ -36494,7 +36494,11 @@
           <t>Proceeds from sale of property and equipment</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E267" t="inlineStr">
         <is>
           <t>-</t>
@@ -41740,7 +41744,11 @@
           <t>Proceeds from disposition of property and equipment</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr"/>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E317" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/VRB.xlsx
+++ b/output/pdf_financials_xlsx/VRB.xlsx
@@ -754,43 +754,43 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.712897</v>
+        <v>0.787897</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.640586</v>
+        <v>0.7155860000000001</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.753386</v>
+        <v>0.842189</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1.088164</v>
+        <v>1.143664</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0.815186</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.37009</v>
+        <v>0.37609</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.237242</v>
+        <v>0.273242</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.117325</v>
+        <v>0.144325</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.131652</v>
+        <v>0.155652</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.143554</v>
+        <v>0.167554</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.217079</v>
+        <v>0.278079</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.184708</v>
+        <v>0.285074</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.296312</v>
+        <v>0.378312</v>
       </c>
       <c r="O7" s="3" t="n">
         <v>0.336368</v>
@@ -1364,10 +1364,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.133467</v>
+        <v>-0.133467</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.01008</v>
+        <v>-0.01008</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>2.871418</v>
@@ -1382,10 +1382,10 @@
         <v>-0</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0.062114</v>
+        <v>-0.062114</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>0.039286</v>
+        <v>-0.039286</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>-0</v>
@@ -4592,10 +4592,10 @@
         <v>0</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.101895</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.048</v>
       </c>
       <c r="F67" s="3" t="n">
         <v>0.489702</v>
@@ -4622,22 +4622,22 @@
         <v>0.765281</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>0.046</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>0</v>
+        <v>0.075</v>
       </c>
       <c r="S67" s="3" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="68">
@@ -7298,34 +7298,34 @@
         <v>0</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.012577</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.003161</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0</v>
+        <v>-0.009971000000000001</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0</v>
+        <v>-0.012495</v>
       </c>
       <c r="L111" s="3" t="n">
-        <v>0</v>
+        <v>-0.004644</v>
       </c>
       <c r="M111" s="3" t="n">
-        <v>0</v>
+        <v>-0.009242</v>
       </c>
       <c r="N111" s="3" t="n">
-        <v>0</v>
+        <v>-0.014933</v>
       </c>
       <c r="O111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002569</v>
       </c>
       <c r="Q111" s="3" t="n">
-        <v>0</v>
+        <v>-0.180788</v>
       </c>
       <c r="R111" s="3" t="n">
         <v>0</v>
@@ -7344,7 +7344,7 @@
         <v>0</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0.002617</v>
+        <v>0</v>
       </c>
       <c r="D112" s="3" t="n">
         <v>0</v>
@@ -8741,34 +8741,34 @@
         <v>0</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.012577</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.003161</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0</v>
+        <v>-0.009971000000000001</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0</v>
+        <v>-0.012495</v>
       </c>
       <c r="L134" s="3" t="n">
-        <v>0</v>
+        <v>-0.004644</v>
       </c>
       <c r="M134" s="3" t="n">
-        <v>0</v>
+        <v>-0.009242</v>
       </c>
       <c r="N134" s="3" t="n">
-        <v>0</v>
+        <v>-0.014933</v>
       </c>
       <c r="O134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002569</v>
       </c>
       <c r="Q134" s="3" t="n">
-        <v>0</v>
+        <v>-0.180788</v>
       </c>
       <c r="R134" s="3" t="n">
         <v>0</v>
@@ -8812,28 +8812,28 @@
         </is>
       </c>
       <c r="J135" s="3" t="n">
-        <v>-0.449639</v>
+        <v>-0.45961</v>
       </c>
       <c r="K135" s="3" t="n">
-        <v>-0.7244</v>
+        <v>-0.736895</v>
       </c>
       <c r="L135" s="3" t="n">
-        <v>-0.784202</v>
+        <v>-0.788846</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>-0.781587</v>
+        <v>-0.790829</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>-1.209294</v>
+        <v>-1.224227</v>
       </c>
       <c r="O135" s="3" t="n">
         <v>-1.232875</v>
       </c>
       <c r="P135" s="3" t="n">
-        <v>-0.61102</v>
+        <v>-0.6135890000000001</v>
       </c>
       <c r="Q135" s="3" t="n">
-        <v>-2.034579</v>
+        <v>-2.215367</v>
       </c>
       <c r="R135" s="3" t="n">
         <v>-0.277644</v>
@@ -25486,7 +25486,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr">
         <is>
           <t>-</t>
@@ -29896,7 +29900,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>-</t>
@@ -33558,7 +33566,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr"/>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E239" t="inlineStr">
         <is>
           <t>-</t>
@@ -39336,7 +39348,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D294" t="inlineStr"/>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E294" t="inlineStr">
         <is>
           <t>-</t>
@@ -40698,7 +40714,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D307" t="inlineStr"/>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E307" s="5" t="n">
         <v>-0.133467</v>
       </c>
@@ -41744,11 +41764,7 @@
           <t>Proceeds from disposition of property and equipment</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>SaleOfPPE</t>
-        </is>
-      </c>
+      <c r="D317" t="inlineStr"/>
       <c r="E317" t="inlineStr">
         <is>
           <t>-</t>
@@ -48970,7 +48986,11 @@
           <t>Directors fees (Note 12)</t>
         </is>
       </c>
-      <c r="D386" t="inlineStr"/>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E386" t="inlineStr">
         <is>
           <t>-</t>
@@ -50340,7 +50360,11 @@
           <t>Directors fees (Note 13)</t>
         </is>
       </c>
-      <c r="D399" t="inlineStr"/>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E399" t="inlineStr">
         <is>
           <t>-</t>
@@ -54086,7 +54110,11 @@
           <t>Directors fees (Note 12)</t>
         </is>
       </c>
-      <c r="D436" t="inlineStr"/>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E436" t="inlineStr">
         <is>
           <t>-</t>
@@ -56922,7 +56950,11 @@
           <t>Directors fees (Note 11)</t>
         </is>
       </c>
-      <c r="D463" t="inlineStr"/>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E463" t="inlineStr">
         <is>
           <t>-</t>
@@ -58708,7 +58740,11 @@
           <t>DEFERRED INCOME TAX RECOVERY</t>
         </is>
       </c>
-      <c r="D480" t="inlineStr"/>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E480" t="inlineStr">
         <is>
           <t>-</t>
@@ -64390,7 +64426,11 @@
           <t>Directors fees</t>
         </is>
       </c>
-      <c r="D534" t="inlineStr"/>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E534" t="inlineStr">
         <is>
           <t>-</t>
@@ -66692,7 +66732,11 @@
           <t>Director fees (Note 11)</t>
         </is>
       </c>
-      <c r="D556" t="inlineStr"/>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E556" t="inlineStr">
         <is>
           <t>-</t>
@@ -70710,7 +70754,11 @@
           <t>Director fees (Note 10)</t>
         </is>
       </c>
-      <c r="D594" t="inlineStr"/>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E594" s="5" t="n">
         <v>0.075</v>
       </c>
@@ -72170,7 +72218,11 @@
           <t>FUTURE INCOME TAX RECOVERY (Note 9)</t>
         </is>
       </c>
-      <c r="D608" t="inlineStr"/>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E608" s="5" t="n">
         <v>0.133467</v>
       </c>
